--- a/Homework/HW1/Q2.xlsx
+++ b/Homework/HW1/Q2.xlsx
@@ -1,10 +1,11 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="4" rupBuild="14420"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="10608"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{24408DF9-10E0-2047-AEFD-E277AAF98705}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="240" yWindow="108" windowWidth="14808" windowHeight="8016"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="18380" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Question X" sheetId="1" r:id="rId1"/>
@@ -14,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18" uniqueCount="18">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="74" uniqueCount="67">
   <si>
     <t>Address</t>
   </si>
@@ -31,49 +32,196 @@
     <t>Comment</t>
   </si>
   <si>
-    <t>1001 000000 000000</t>
-  </si>
-  <si>
-    <t>1001 000001 001010</t>
-  </si>
-  <si>
-    <t>904A</t>
-  </si>
-  <si>
-    <t>mov R0, 0</t>
-  </si>
-  <si>
-    <t>mov R1, 10</t>
-  </si>
-  <si>
-    <t>R0 holds 0</t>
-  </si>
-  <si>
-    <t>R1 hold 10</t>
-  </si>
-  <si>
     <t>Hex String</t>
   </si>
   <si>
-    <t>9000904A</t>
-  </si>
-  <si>
-    <t>3. ONLY HAVE ONE ENTRY FOR THE HEX STRING</t>
-  </si>
-  <si>
-    <t>4. WE SHOULD BE ABLE TO COPY THE ASSEMBLY FILE COLUMN AND RUN IT IN THE SIMULATOR</t>
-  </si>
-  <si>
-    <t>1. NOTE THIS IS AN EXAMPLE; ERASE THE TWO SAMPLE ROWS AND THESE COMMENTS BEFORE YOU SUBMIT</t>
-  </si>
-  <si>
-    <t>2. YOU SHOULD HAVE ONE EXCEL FILE PER QUESTION</t>
+    <t>mov R5, 1</t>
+  </si>
+  <si>
+    <t>mov R0, [R5]</t>
+  </si>
+  <si>
+    <t>inc R5</t>
+  </si>
+  <si>
+    <t>R5 holds 1</t>
+  </si>
+  <si>
+    <t>R5 holds 1+1 = 2</t>
+  </si>
+  <si>
+    <t>mov R1, [R5]</t>
+  </si>
+  <si>
+    <t>copy the value in memory address 1 to R0</t>
+  </si>
+  <si>
+    <t>R5 holds 2+1 = 3</t>
+  </si>
+  <si>
+    <t>mov R3, [R5]</t>
+  </si>
+  <si>
+    <t>R5 hols 3+1 = 4</t>
+  </si>
+  <si>
+    <t>copy the value in memory address 2 to R1</t>
+  </si>
+  <si>
+    <t>copy the value in memory address 3 to R2</t>
+  </si>
+  <si>
+    <t>copy the value in memory address 4 to R3</t>
+  </si>
+  <si>
+    <t>mov R2, [R5]</t>
+  </si>
+  <si>
+    <t>cmp R1, R5</t>
+  </si>
+  <si>
+    <t>mov R5, 0</t>
+  </si>
+  <si>
+    <t>R5 holds 0</t>
+  </si>
+  <si>
+    <t>mov R4, 0</t>
+  </si>
+  <si>
+    <t>add R4, R0</t>
+  </si>
+  <si>
+    <t>add R4, R2</t>
+  </si>
+  <si>
+    <t>R4 holds 0 for holding the results</t>
+  </si>
+  <si>
+    <t>R0 get the addition of the content in R4 and content in R0</t>
+  </si>
+  <si>
+    <t>sub R4, R3</t>
+  </si>
+  <si>
+    <t>increment R5</t>
+  </si>
+  <si>
+    <t>jne 53</t>
+  </si>
+  <si>
+    <t>if R5 not equal to R1, not equal jump to 53, which add R4 by R0 again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">compare if R5 is equal to R1, value b, </t>
+  </si>
+  <si>
+    <t>add c</t>
+  </si>
+  <si>
+    <t>subtract d</t>
+  </si>
+  <si>
+    <t>subtract d again, which means subtract 2d</t>
+  </si>
+  <si>
+    <t>mov R5, 10</t>
+  </si>
+  <si>
+    <t>mov [R5], R4</t>
+  </si>
+  <si>
+    <t>R5 holds 10</t>
+  </si>
+  <si>
+    <t>store the result in R4 to memory address 10</t>
+  </si>
+  <si>
+    <t>c005</t>
+  </si>
+  <si>
+    <t>c045</t>
+  </si>
+  <si>
+    <t>c085</t>
+  </si>
+  <si>
+    <t>c0c5</t>
+  </si>
+  <si>
+    <t>914a</t>
+  </si>
+  <si>
+    <t>b144</t>
+  </si>
+  <si>
+    <t>halt</t>
+  </si>
+  <si>
+    <t>stop the program</t>
+  </si>
+  <si>
+    <t>0000</t>
+  </si>
+  <si>
+    <t>9141c0051005c0451005c0851005c0c5910091405100100580453035510261036103914ab1440000</t>
+  </si>
+  <si>
+    <t>1001 000101 000001</t>
+  </si>
+  <si>
+    <t>1100 000000 000101</t>
+  </si>
+  <si>
+    <t xml:space="preserve">0001 000000 000101 </t>
+  </si>
+  <si>
+    <t>1100 000001 000101</t>
+  </si>
+  <si>
+    <t>0001 000000 000101</t>
+  </si>
+  <si>
+    <t>1100 000010 000101</t>
+  </si>
+  <si>
+    <t>1100 000011 000101</t>
+  </si>
+  <si>
+    <t>1001 000100 000000</t>
+  </si>
+  <si>
+    <t>1001 000101 000000</t>
+  </si>
+  <si>
+    <t>0101 000100 000000</t>
+  </si>
+  <si>
+    <t>1000 000001 000101</t>
+  </si>
+  <si>
+    <t>0011 000000 110101</t>
+  </si>
+  <si>
+    <t>0101 000100 000010</t>
+  </si>
+  <si>
+    <t>0110 000100 000011</t>
+  </si>
+  <si>
+    <t>1001 000101 001010</t>
+  </si>
+  <si>
+    <t>1011 000101 000100</t>
+  </si>
+  <si>
+    <t>0000 000000 000000</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <fonts count="4" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -86,23 +234,21 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Courier New"/>
-      <family val="3"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
       <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
     </font>
   </fonts>
   <fills count="2">
@@ -125,26 +271,18 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="justify" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -163,9 +301,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -203,9 +341,9 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
-        <a:latin typeface="Cambria" panose="020F0302020204030204"/>
+        <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -240,7 +378,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
+        <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
         <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
@@ -275,7 +413,7 @@
         <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -448,19 +586,21 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:G21"/>
+  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14" x14ac:dyDescent="0.15"/>
   <cols>
-    <col min="1" max="1" width="12.109375" customWidth="1"/>
-    <col min="2" max="2" width="24.88671875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.44140625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="15.6640625" customWidth="1"/>
-    <col min="5" max="5" width="15.33203125" customWidth="1"/>
-    <col min="7" max="7" width="97.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.1640625" style="2" customWidth="1"/>
+    <col min="2" max="2" width="24.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="15.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="55.5" style="2" customWidth="1"/>
+    <col min="6" max="6" width="8.83203125" style="2"/>
+    <col min="7" max="7" width="97.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="8.83203125" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.15">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -477,66 +617,355 @@
         <v>4</v>
       </c>
       <c r="G1" s="1" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="15" x14ac:dyDescent="0.15">
+      <c r="A2" s="2">
+        <v>43</v>
+      </c>
+      <c r="B2" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="C2" s="2">
+        <v>9141</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>6</v>
+      </c>
+      <c r="E2" s="2" t="s">
+        <v>9</v>
+      </c>
+      <c r="G2" s="4" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A3" s="2">
+        <v>44</v>
+      </c>
+      <c r="B3" s="2" t="s">
+        <v>51</v>
+      </c>
+      <c r="C3" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D3" s="2" t="s">
+        <v>7</v>
+      </c>
+      <c r="E3" s="2" t="s">
         <v>12</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="4">
+      <c r="G3" s="5"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A4" s="2">
+        <v>45</v>
+      </c>
+      <c r="B4" s="2" t="s">
+        <v>52</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E4" s="2" t="s">
+        <v>10</v>
+      </c>
+      <c r="G4" s="5"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A5" s="2">
+        <v>46</v>
+      </c>
+      <c r="B5" s="2" t="s">
+        <v>53</v>
+      </c>
+      <c r="C5" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="G5" s="5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A6" s="2">
+        <v>47</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E6" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="G6" s="5"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A7" s="2">
+        <v>48</v>
+      </c>
+      <c r="B7" s="2" t="s">
+        <v>55</v>
+      </c>
+      <c r="C7" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E7" s="2" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A8" s="2">
+        <v>49</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C8" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A9" s="2">
+        <v>50</v>
+      </c>
+      <c r="B9" s="2" t="s">
+        <v>56</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D9" s="2" t="s">
+        <v>14</v>
+      </c>
+      <c r="E9" s="2" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A10" s="2">
+        <v>51</v>
+      </c>
+      <c r="B10" s="2" t="s">
+        <v>57</v>
+      </c>
+      <c r="C10" s="2">
+        <v>9100</v>
+      </c>
+      <c r="D10" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E10" s="2" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A11" s="2">
+        <v>52</v>
+      </c>
+      <c r="B11" s="2" t="s">
+        <v>58</v>
+      </c>
+      <c r="C11" s="2">
+        <v>9140</v>
+      </c>
+      <c r="D11" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A12" s="2">
+        <v>53</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>59</v>
+      </c>
+      <c r="C12" s="2">
+        <v>5100</v>
+      </c>
+      <c r="D12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="E12" s="2" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A13" s="2">
+        <v>54</v>
+      </c>
+      <c r="B13" s="2" t="s">
+        <v>54</v>
+      </c>
+      <c r="C13" s="2">
+        <v>1005</v>
+      </c>
+      <c r="D13" s="2" t="s">
+        <v>8</v>
+      </c>
+      <c r="E13" s="2" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A14" s="2">
+        <v>55</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>60</v>
+      </c>
+      <c r="C14" s="2">
+        <v>8045</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A15" s="2">
+        <v>56</v>
+      </c>
+      <c r="B15" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C15" s="2">
+        <v>3035</v>
+      </c>
+      <c r="D15" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E15" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="B2" s="3" t="s">
-        <v>5</v>
-      </c>
-      <c r="C2" s="3">
-        <v>9000</v>
-      </c>
-      <c r="D2" s="5" t="s">
-        <v>8</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>10</v>
-      </c>
-      <c r="G2" s="7" t="s">
-        <v>13</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="4">
-        <v>32</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>6</v>
-      </c>
-      <c r="C3" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="D3" s="5" t="s">
-        <v>9</v>
-      </c>
-      <c r="E3" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="G3" s="8" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G4" s="8" t="s">
-        <v>17</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G5" s="8" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="G6" s="8" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="E9" s="6"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.15">
+      <c r="A16" s="2">
+        <v>57</v>
+      </c>
+      <c r="B16" s="2" t="s">
+        <v>62</v>
+      </c>
+      <c r="C16" s="2">
+        <v>5102</v>
+      </c>
+      <c r="D16" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E16" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A17" s="2">
+        <v>58</v>
+      </c>
+      <c r="B17" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C17" s="2">
+        <v>6103</v>
+      </c>
+      <c r="D17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E17" s="2" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A18" s="2">
+        <v>59</v>
+      </c>
+      <c r="B18" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="C18" s="2">
+        <v>6103</v>
+      </c>
+      <c r="D18" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="E18" s="2" t="s">
+        <v>35</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A19" s="2">
+        <v>60</v>
+      </c>
+      <c r="B19" s="2" t="s">
+        <v>64</v>
+      </c>
+      <c r="C19" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="D19" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="E19" s="2" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A20" s="2">
+        <v>61</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>65</v>
+      </c>
+      <c r="C20" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>39</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.15">
+      <c r="A21" s="2">
+        <v>62</v>
+      </c>
+      <c r="B21" s="2" t="s">
+        <v>66</v>
+      </c>
+      <c r="C21" s="6" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E21" s="2" t="s">
+        <v>47</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
